--- a/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T0860_W0027F0001T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>55.03006984245024</v>
+        <v>8.942386349398165</v>
       </c>
       <c r="D2" t="n">
-        <v>55.08275662585293</v>
+        <v>8.950947951701101</v>
       </c>
       <c r="E2" t="n">
-        <v>9.80450650298379</v>
+        <v>1.593232306734866</v>
       </c>
       <c r="F2" t="n">
-        <v>9.84756667257858</v>
+        <v>1.600229584294019</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.04881347006023</v>
+        <v>4.882932188884787</v>
       </c>
       <c r="D3" t="n">
-        <v>30.05103777545412</v>
+        <v>4.883293638511295</v>
       </c>
       <c r="E3" t="n">
-        <v>9.80450650298379</v>
+        <v>1.593232306734866</v>
       </c>
       <c r="F3" t="n">
-        <v>9.84756667257858</v>
+        <v>1.600229584294019</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.1871747389813</v>
+        <v>7.667915895084461</v>
       </c>
       <c r="D4" t="n">
-        <v>47.28355102263627</v>
+        <v>7.683577041178394</v>
       </c>
       <c r="E4" t="n">
-        <v>9.80450650298379</v>
+        <v>1.593232306734866</v>
       </c>
       <c r="F4" t="n">
-        <v>9.84756667257858</v>
+        <v>1.600229584294019</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.88875098342587</v>
+        <v>8.594422034806705</v>
       </c>
       <c r="D5" t="n">
-        <v>53.066495321651</v>
+        <v>8.623305489768288</v>
       </c>
       <c r="E5" t="n">
-        <v>9.80450650298379</v>
+        <v>1.593232306734866</v>
       </c>
       <c r="F5" t="n">
-        <v>9.84756667257858</v>
+        <v>1.600229584294019</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
